--- a/CÔNG TY TNHH CÔNG NGHỆ KIM LOẠI APEX/Thong tin cty APEX.xlsx
+++ b/CÔNG TY TNHH CÔNG NGHỆ KIM LOẠI APEX/Thong tin cty APEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LanNgo_Projects\HoSoDoanhNghiep\CÔNG TY TNHH CÔNG NGHỆ KIM LOẠI APEX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF886C62-088C-4385-8F3D-F31BAE125A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48858A8-70A3-47B2-A56E-B638B5EAB0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D04982A-E4C4-478F-8127-759B5EC1EFFD}"/>
   </bookViews>
@@ -37,14 +37,6 @@
     <t>ĐỊA CHỈ</t>
   </si>
   <si>
-    <t>Tên tiếng Việt: Công ty TNHH Công Nghệ Kim Loại Apex.
-Tên tiếng Anh: Apex Metal Technology Co., Ltd.
-Tên viết tắt: Apex Metal Tech</t>
-  </si>
-  <si>
-    <t>Số 145/29 đường Phú An 024, khu phố Phú Thứ, Phường Phú An, TP Hồ Chí Minh, Việt Nam</t>
-  </si>
-  <si>
     <t>VỒN ĐIỀU LỆ</t>
   </si>
   <si>
@@ -142,6 +134,14 @@
   </si>
   <si>
     <t>NGƯỜI ĐẠI DIỆN Pháp luật</t>
+  </si>
+  <si>
+    <t>Tên tiếng Việt: CÔNG TY TNHH CÔNG NGHỆ KIM LOẠI APEX
+Tên tiếng Anh: APEX METAL TECHNOLOGY CO., LTD
+Tên viết tắt: APEX METAL TECH</t>
+  </si>
+  <si>
+    <t>Số 145/29 đường Phú An 024, khu phố Phú Thứ, Phường Phú An, Thành phố Hồ Chí Minh, Việt Nam; Số điện thoại: 0919498839</t>
   </si>
 </sst>
 </file>
@@ -394,7 +394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -412,9 +412,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -797,66 +794,66 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="10"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="B5" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="18"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="11"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="B7" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>4</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="19"/>
-      <c r="B6" s="14"/>
-    </row>
-    <row r="7" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -864,49 +861,49 @@
         <v>2420</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="22">
+        <v>2592</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="23"/>
+      <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="23">
-        <v>2592</v>
-      </c>
-      <c r="B13" s="7" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="22">
+        <v>2599</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="7" t="s">
+    <row r="16" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="23"/>
+      <c r="B16" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="23">
-        <v>2599</v>
-      </c>
-      <c r="B15" s="7" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="22">
+        <v>4329</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
-      <c r="B16" s="7" t="s">
+    <row r="18" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="7" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="23">
-        <v>4329</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
-      <c r="B18" s="7" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -914,63 +911,63 @@
         <v>4330</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="22">
+        <v>4673</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="23"/>
+      <c r="B21" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="23">
-        <v>4673</v>
-      </c>
-      <c r="B20" s="7" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="22">
+        <v>4679</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="7" t="s">
+    <row r="23" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="23"/>
+      <c r="B23" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="23">
-        <v>4679</v>
-      </c>
-      <c r="B22" s="7" t="s">
+    <row r="24" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="22">
+        <v>4752</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24"/>
-      <c r="B23" s="7" t="s">
+    <row r="25" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="23"/>
+      <c r="B25" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="23">
-        <v>4752</v>
-      </c>
-      <c r="B24" s="7" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="22">
+        <v>4773</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="24"/>
-      <c r="B25" s="7" t="s">
+    <row r="27" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="23"/>
+      <c r="B27" s="7" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="23">
-        <v>4773</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24"/>
-      <c r="B27" s="7" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -978,21 +975,21 @@
         <v>6810</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="22">
+        <v>7710</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="23"/>
+      <c r="B30" s="7" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="23">
-        <v>7710</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24"/>
-      <c r="B30" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1000,7 +997,7 @@
         <v>7911</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1008,15 +1005,15 @@
         <v>8121</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>8210</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>31</v>
+      <c r="B33" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1055,6 @@
     <hyperlink ref="A32" r:id="rId25" display="https://masothue.com/tra-cuu-ma-so-thue-theo-nganh-nghe/ve-sinh-chung-nha-cua-8121" xr:uid="{12FC075E-A02C-425C-A81F-8127AD70085B}"/>
     <hyperlink ref="B32" r:id="rId26" display="https://masothue.com/tra-cuu-ma-so-thue-theo-nganh-nghe/ve-sinh-chung-nha-cua-8121" xr:uid="{411D19A1-5BED-4FC5-95FC-7EE3972F1D0B}"/>
     <hyperlink ref="A33" r:id="rId27" display="https://masothue.com/tra-cuu-ma-so-thue-theo-nganh-nghe/hoat-dong-hanh-chinh-va-ho-tro-van-phong-8210" xr:uid="{B701AEA6-527F-49D3-B759-C3C59FDF8A32}"/>
-    <hyperlink ref="B33" r:id="rId28" display="https://masothue.com/tra-cuu-ma-so-thue-theo-nganh-nghe/hoat-dong-hanh-chinh-va-ho-tro-van-phong-8210" xr:uid="{1EF870C1-B951-42AE-88BE-67A98B496FA6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1071,7 +1067,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
